--- a/data/WP17/wp17_uebersicht.xlsx
+++ b/data/WP17/wp17_uebersicht.xlsx
@@ -387,7 +387,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>3900</v>
+        <v>4343</v>
       </c>
     </row>
     <row r="5">
@@ -395,7 +395,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>40.1932218984818</v>
+        <v>33.3997853090017</v>
       </c>
     </row>
   </sheetData>
@@ -632,13 +632,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5247E649-AFDC-4F82-9B27-36F881C9F5EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D8A79D1-7FEE-43B9-8B8C-F85297925A8F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69D755AE-2151-46C3-B4B7-1E1F027A175C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F6EC455-15E1-41C4-B8CC-8CE57CC0B656}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{925D1686-80DC-4DE1-AC25-FD1D53DF48DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3F021C2-0A13-45A7-B525-D3D5F057A05F}"/>
 </file>